--- a/artfynd/A 41571-2024 artfynd.xlsx
+++ b/artfynd/A 41571-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,6 +787,567 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122918582</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57631</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>A 41571, Kärrebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>589545</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6415568</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Även sjungande</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122918624</v>
+      </c>
+      <c r="B4" t="n">
+        <v>95128</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 41571, Kärrebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>589498</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6415570</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122918696</v>
+      </c>
+      <c r="B5" t="n">
+        <v>95128</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 41571, Kärrebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>589462</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6415594</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122918503</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90964</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 41571, Kärrebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>589407</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6415632</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122918444</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92225</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 41571, Kärrebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>589466</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6415553</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41571-2024 artfynd.xlsx
+++ b/artfynd/A 41571-2024 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122918582</v>
+        <v>122918624</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>95128</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,39 +802,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,13 +834,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589545</v>
+        <v>589498</v>
       </c>
       <c r="R3" t="n">
-        <v>6415568</v>
+        <v>6415570</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,17 +872,13 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Även sjungande</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -909,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122918624</v>
+        <v>122918582</v>
       </c>
       <c r="B4" t="n">
-        <v>95128</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,31 +909,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -953,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589498</v>
+        <v>589545</v>
       </c>
       <c r="R4" t="n">
-        <v>6415570</v>
+        <v>6415568</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,13 +987,17 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Även sjungande</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122918503</v>
+        <v>122918444</v>
       </c>
       <c r="B6" t="n">
-        <v>90964</v>
+        <v>92225</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,30 +1135,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1174,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589407</v>
+        <v>589466</v>
       </c>
       <c r="R6" t="n">
-        <v>6415632</v>
+        <v>6415553</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122918444</v>
+        <v>122918503</v>
       </c>
       <c r="B7" t="n">
-        <v>92225</v>
+        <v>90964</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1249,30 +1249,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589466</v>
+        <v>589407</v>
       </c>
       <c r="R7" t="n">
-        <v>6415553</v>
+        <v>6415632</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 41571-2024 artfynd.xlsx
+++ b/artfynd/A 41571-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122900739</v>
       </c>
       <c r="B2" t="n">
-        <v>95128</v>
+        <v>95136</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>122918624</v>
       </c>
       <c r="B3" t="n">
-        <v>95128</v>
+        <v>95136</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122918582</v>
+        <v>122918696</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>95136</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,39 +909,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -949,13 +941,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589545</v>
+        <v>589462</v>
       </c>
       <c r="R4" t="n">
-        <v>6415568</v>
+        <v>6415594</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,17 +979,13 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Även sjungande</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1016,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122918696</v>
+        <v>122918503</v>
       </c>
       <c r="B5" t="n">
-        <v>95128</v>
+        <v>90972</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,31 +1016,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1060,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589462</v>
+        <v>589407</v>
       </c>
       <c r="R5" t="n">
-        <v>6415594</v>
+        <v>6415632</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122918444</v>
+        <v>122918582</v>
       </c>
       <c r="B6" t="n">
-        <v>92225</v>
+        <v>57631</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,38 +1130,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1174,13 +1170,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589466</v>
+        <v>589545</v>
       </c>
       <c r="R6" t="n">
-        <v>6415553</v>
+        <v>6415568</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,13 +1208,17 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Även sjungande</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122918503</v>
+        <v>122918444</v>
       </c>
       <c r="B7" t="n">
-        <v>90964</v>
+        <v>92233</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1249,30 +1249,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589407</v>
+        <v>589466</v>
       </c>
       <c r="R7" t="n">
-        <v>6415632</v>
+        <v>6415553</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 41571-2024 artfynd.xlsx
+++ b/artfynd/A 41571-2024 artfynd.xlsx
@@ -783,17 +783,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122918624</v>
+        <v>122918444</v>
       </c>
       <c r="B3" t="n">
-        <v>95136</v>
+        <v>92233</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,27 +806,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589498</v>
+        <v>589466</v>
       </c>
       <c r="R3" t="n">
-        <v>6415570</v>
+        <v>6415553</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122918696</v>
+        <v>122918503</v>
       </c>
       <c r="B4" t="n">
-        <v>95136</v>
+        <v>90972</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,31 +916,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -941,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589462</v>
+        <v>589407</v>
       </c>
       <c r="R4" t="n">
-        <v>6415594</v>
+        <v>6415632</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122918503</v>
+        <v>122918696</v>
       </c>
       <c r="B5" t="n">
-        <v>90972</v>
+        <v>95136</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,38 +1030,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1055,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589407</v>
+        <v>589462</v>
       </c>
       <c r="R5" t="n">
-        <v>6415632</v>
+        <v>6415594</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122918582</v>
+        <v>122918624</v>
       </c>
       <c r="B6" t="n">
-        <v>57631</v>
+        <v>95136</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,39 +1137,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1170,13 +1169,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589545</v>
+        <v>589498</v>
       </c>
       <c r="R6" t="n">
-        <v>6415568</v>
+        <v>6415570</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,17 +1207,13 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Även sjungande</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1237,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122918444</v>
+        <v>122918582</v>
       </c>
       <c r="B7" t="n">
-        <v>92233</v>
+        <v>57631</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1249,38 +1244,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1288,13 +1284,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589466</v>
+        <v>589545</v>
       </c>
       <c r="R7" t="n">
-        <v>6415553</v>
+        <v>6415568</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1326,13 +1322,17 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Även sjungande</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41571-2024 artfynd.xlsx
+++ b/artfynd/A 41571-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122900739</v>
+        <v>122918582</v>
       </c>
       <c r="B2" t="n">
-        <v>95136</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,53 +687,53 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kärrebo 1:6, Sm</t>
+          <t>A 41571, Kärrebo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589481</v>
+        <v>589545</v>
       </c>
       <c r="R2" t="n">
-        <v>6415768</v>
+        <v>6415568</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,12 +757,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Även sjungande</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,19 +776,18 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -1018,7 +1022,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122918696</v>
+        <v>122918624</v>
       </c>
       <c r="B5" t="n">
         <v>95136</v>
@@ -1062,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589462</v>
+        <v>589498</v>
       </c>
       <c r="R5" t="n">
-        <v>6415594</v>
+        <v>6415570</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,7 +1129,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122918624</v>
+        <v>122918696</v>
       </c>
       <c r="B6" t="n">
         <v>95136</v>
@@ -1169,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589498</v>
+        <v>589462</v>
       </c>
       <c r="R6" t="n">
-        <v>6415570</v>
+        <v>6415594</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122918582</v>
+        <v>122900739</v>
       </c>
       <c r="B7" t="n">
-        <v>57631</v>
+        <v>95136</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,53 +1248,53 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 41571, Kärrebo, Sm</t>
+          <t>Kärrebo 1:6, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589545</v>
+        <v>589481</v>
       </c>
       <c r="R7" t="n">
-        <v>6415568</v>
+        <v>6415768</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,17 +1318,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Även sjungande</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1333,18 +1332,19 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Gunilla Nilsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 41571-2024 artfynd.xlsx
+++ b/artfynd/A 41571-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122918582</v>
+        <v>122918696</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>95136</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589545</v>
+        <v>589462</v>
       </c>
       <c r="R2" t="n">
-        <v>6415568</v>
+        <v>6415594</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,17 +757,13 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Även sjungande</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -908,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122918503</v>
+        <v>122918582</v>
       </c>
       <c r="B4" t="n">
-        <v>90972</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,21 +912,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -946,12 +934,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -959,13 +948,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589407</v>
+        <v>589545</v>
       </c>
       <c r="R4" t="n">
-        <v>6415632</v>
+        <v>6415568</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,13 +986,17 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Även sjungande</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1129,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122918696</v>
+        <v>122918503</v>
       </c>
       <c r="B6" t="n">
-        <v>95136</v>
+        <v>90972</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,31 +1134,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589462</v>
+        <v>589407</v>
       </c>
       <c r="R6" t="n">
-        <v>6415594</v>
+        <v>6415632</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 41571-2024 artfynd.xlsx
+++ b/artfynd/A 41571-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122918696</v>
+        <v>122918624</v>
       </c>
       <c r="B2" t="n">
-        <v>95136</v>
+        <v>95139</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589462</v>
+        <v>589498</v>
       </c>
       <c r="R2" t="n">
-        <v>6415594</v>
+        <v>6415570</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122918444</v>
+        <v>122918582</v>
       </c>
       <c r="B3" t="n">
-        <v>92233</v>
+        <v>57634</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,38 +794,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,13 +834,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589466</v>
+        <v>589545</v>
       </c>
       <c r="R3" t="n">
-        <v>6415553</v>
+        <v>6415568</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,13 +872,17 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Även sjungande</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122918582</v>
+        <v>122918503</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>90975</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,21 +917,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -934,13 +939,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,13 +952,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589545</v>
+        <v>589407</v>
       </c>
       <c r="R4" t="n">
-        <v>6415568</v>
+        <v>6415632</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,17 +990,13 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Även sjungande</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122918624</v>
+        <v>122918444</v>
       </c>
       <c r="B5" t="n">
-        <v>95136</v>
+        <v>92236</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,27 +1031,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589498</v>
+        <v>589466</v>
       </c>
       <c r="R5" t="n">
-        <v>6415570</v>
+        <v>6415553</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122918503</v>
+        <v>122918696</v>
       </c>
       <c r="B6" t="n">
-        <v>90972</v>
+        <v>95139</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,38 +1141,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589407</v>
+        <v>589462</v>
       </c>
       <c r="R6" t="n">
-        <v>6415632</v>
+        <v>6415594</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1239,7 +1239,7 @@
         <v>122900739</v>
       </c>
       <c r="B7" t="n">
-        <v>95136</v>
+        <v>95139</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 41571-2024 artfynd.xlsx
+++ b/artfynd/A 41571-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122918624</v>
+        <v>122918444</v>
       </c>
       <c r="B2" t="n">
-        <v>95139</v>
+        <v>92238</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589498</v>
+        <v>589466</v>
       </c>
       <c r="R2" t="n">
-        <v>6415570</v>
+        <v>6415553</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122918582</v>
+        <v>122918503</v>
       </c>
       <c r="B3" t="n">
-        <v>57634</v>
+        <v>90977</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +805,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,13 +827,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589545</v>
+        <v>589407</v>
       </c>
       <c r="R3" t="n">
-        <v>6415568</v>
+        <v>6415632</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,17 +878,13 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Även sjungande</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -901,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122918503</v>
+        <v>122918582</v>
       </c>
       <c r="B4" t="n">
-        <v>90975</v>
+        <v>57634</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,12 +941,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -952,13 +955,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589407</v>
+        <v>589545</v>
       </c>
       <c r="R4" t="n">
-        <v>6415632</v>
+        <v>6415568</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,13 +993,17 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Även sjungande</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1015,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122918444</v>
+        <v>122918624</v>
       </c>
       <c r="B5" t="n">
-        <v>92236</v>
+        <v>95141</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,34 +1038,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589466</v>
+        <v>589498</v>
       </c>
       <c r="R5" t="n">
-        <v>6415553</v>
+        <v>6415570</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,7 +1132,7 @@
         <v>122918696</v>
       </c>
       <c r="B6" t="n">
-        <v>95139</v>
+        <v>95141</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>122900739</v>
       </c>
       <c r="B7" t="n">
-        <v>95139</v>
+        <v>95141</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 41571-2024 artfynd.xlsx
+++ b/artfynd/A 41571-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122918444</v>
+        <v>122918696</v>
       </c>
       <c r="B2" t="n">
-        <v>92238</v>
+        <v>95147</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589466</v>
+        <v>589462</v>
       </c>
       <c r="R2" t="n">
-        <v>6415553</v>
+        <v>6415594</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -792,7 +785,7 @@
         <v>122918503</v>
       </c>
       <c r="B3" t="n">
-        <v>90977</v>
+        <v>90983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -903,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122918582</v>
+        <v>122918624</v>
       </c>
       <c r="B4" t="n">
-        <v>57634</v>
+        <v>95147</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +908,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -955,13 +940,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589545</v>
+        <v>589498</v>
       </c>
       <c r="R4" t="n">
-        <v>6415568</v>
+        <v>6415570</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,17 +978,13 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Även sjungande</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1022,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122918624</v>
+        <v>122918444</v>
       </c>
       <c r="B5" t="n">
-        <v>95141</v>
+        <v>92244</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,27 +1019,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1066,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589498</v>
+        <v>589466</v>
       </c>
       <c r="R5" t="n">
-        <v>6415570</v>
+        <v>6415553</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122918696</v>
+        <v>122918582</v>
       </c>
       <c r="B6" t="n">
-        <v>95141</v>
+        <v>57634</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,31 +1129,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1173,13 +1169,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589462</v>
+        <v>589545</v>
       </c>
       <c r="R6" t="n">
-        <v>6415594</v>
+        <v>6415568</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,13 +1207,17 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Även sjungande</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>122900739</v>
       </c>
       <c r="B7" t="n">
-        <v>95141</v>
+        <v>95147</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 41571-2024 artfynd.xlsx
+++ b/artfynd/A 41571-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122918696</v>
+        <v>122918444</v>
       </c>
       <c r="B2" t="n">
-        <v>95147</v>
+        <v>92247</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589462</v>
+        <v>589466</v>
       </c>
       <c r="R2" t="n">
-        <v>6415594</v>
+        <v>6415553</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122918503</v>
+        <v>122918582</v>
       </c>
       <c r="B3" t="n">
-        <v>90983</v>
+        <v>57634</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +805,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,12 +827,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589407</v>
+        <v>589545</v>
       </c>
       <c r="R3" t="n">
-        <v>6415632</v>
+        <v>6415568</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,13 +879,17 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Även sjungande</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122918624</v>
+        <v>122918696</v>
       </c>
       <c r="B4" t="n">
-        <v>95147</v>
+        <v>95150</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589498</v>
+        <v>589462</v>
       </c>
       <c r="R4" t="n">
-        <v>6415570</v>
+        <v>6415594</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122918444</v>
+        <v>122918503</v>
       </c>
       <c r="B5" t="n">
-        <v>92244</v>
+        <v>90986</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,30 +1027,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1054,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589466</v>
+        <v>589407</v>
       </c>
       <c r="R5" t="n">
-        <v>6415553</v>
+        <v>6415632</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122918582</v>
+        <v>122918624</v>
       </c>
       <c r="B6" t="n">
-        <v>57634</v>
+        <v>95150</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,39 +1141,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1169,13 +1173,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589545</v>
+        <v>589498</v>
       </c>
       <c r="R6" t="n">
-        <v>6415568</v>
+        <v>6415570</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,17 +1211,13 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Även sjungande</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>122900739</v>
       </c>
       <c r="B7" t="n">
-        <v>95147</v>
+        <v>95150</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 41571-2024 artfynd.xlsx
+++ b/artfynd/A 41571-2024 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122918582</v>
+        <v>122918696</v>
       </c>
       <c r="B3" t="n">
-        <v>57634</v>
+        <v>95150</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,39 +801,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,13 +833,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589545</v>
+        <v>589462</v>
       </c>
       <c r="R3" t="n">
-        <v>6415568</v>
+        <v>6415594</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,17 +871,13 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Även sjungande</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -908,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122918696</v>
+        <v>122918582</v>
       </c>
       <c r="B4" t="n">
-        <v>95150</v>
+        <v>57634</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,31 +908,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -952,13 +948,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589462</v>
+        <v>589545</v>
       </c>
       <c r="R4" t="n">
-        <v>6415594</v>
+        <v>6415568</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,13 +986,17 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Även sjungande</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41571-2024 artfynd.xlsx
+++ b/artfynd/A 41571-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122918444</v>
+        <v>122918624</v>
       </c>
       <c r="B2" t="n">
-        <v>92247</v>
+        <v>95167</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589466</v>
+        <v>589498</v>
       </c>
       <c r="R2" t="n">
-        <v>6415553</v>
+        <v>6415570</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122918696</v>
+        <v>122918582</v>
       </c>
       <c r="B3" t="n">
-        <v>95150</v>
+        <v>57640</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,31 +794,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,13 +834,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589462</v>
+        <v>589545</v>
       </c>
       <c r="R3" t="n">
-        <v>6415594</v>
+        <v>6415568</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,13 +872,17 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Även sjungande</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122918582</v>
+        <v>122918696</v>
       </c>
       <c r="B4" t="n">
-        <v>57634</v>
+        <v>95167</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,39 +913,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,13 +945,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589545</v>
+        <v>589462</v>
       </c>
       <c r="R4" t="n">
-        <v>6415568</v>
+        <v>6415594</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,17 +983,13 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Även sjungande</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1018,7 +1011,7 @@
         <v>122918503</v>
       </c>
       <c r="B5" t="n">
-        <v>90986</v>
+        <v>91003</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1129,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122918624</v>
+        <v>122918444</v>
       </c>
       <c r="B6" t="n">
-        <v>95150</v>
+        <v>92264</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,27 +1138,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589498</v>
+        <v>589466</v>
       </c>
       <c r="R6" t="n">
-        <v>6415570</v>
+        <v>6415553</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1239,7 +1239,7 @@
         <v>122900739</v>
       </c>
       <c r="B7" t="n">
-        <v>95150</v>
+        <v>95167</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 41571-2024 artfynd.xlsx
+++ b/artfynd/A 41571-2024 artfynd.xlsx
@@ -1239,7 +1239,7 @@
         <v>122900739</v>
       </c>
       <c r="B7" t="n">
-        <v>95167</v>
+        <v>95173</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 41571-2024 artfynd.xlsx
+++ b/artfynd/A 41571-2024 artfynd.xlsx
@@ -1239,7 +1239,7 @@
         <v>122900739</v>
       </c>
       <c r="B7" t="n">
-        <v>95173</v>
+        <v>95175</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 41571-2024 artfynd.xlsx
+++ b/artfynd/A 41571-2024 artfynd.xlsx
@@ -1239,7 +1239,7 @@
         <v>122900739</v>
       </c>
       <c r="B7" t="n">
-        <v>95175</v>
+        <v>95683</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
